--- a/output/yearly_benthic_cover_iteration_67_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_67_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.23015548340914</v>
+        <v>45.33047421029313</v>
       </c>
       <c r="M2" t="n">
-        <v>99.59718589628224</v>
+        <v>100.0191087381132</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.94871468737968</v>
+        <v>88.03687563122104</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92260087366014</v>
+        <v>45.95358149053691</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228533457122558</v>
+        <v>2.228736271997047</v>
       </c>
       <c r="E3" t="n">
-        <v>5.698454135864377</v>
+        <v>5.721007473542237</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428444857075193</v>
+        <v>0.7429120906656823</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97185645673773</v>
+        <v>33.98168328718325</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17084634254588</v>
+        <v>34.17395617062138</v>
       </c>
       <c r="I3" t="n">
-        <v>6.493401773729611</v>
+        <v>6.545379770550918</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642778035671995</v>
+        <v>4.643200566660514</v>
       </c>
       <c r="K3" t="n">
-        <v>12.05128531262033</v>
+        <v>11.96312436877897</v>
       </c>
       <c r="L3" t="n">
-        <v>48.79301336811567</v>
+        <v>48.84834916840399</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7668995543961</v>
+        <v>106.7650550277199</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.91644076406919</v>
+        <v>87.15918984058713</v>
       </c>
       <c r="C4" t="n">
-        <v>42.51127596958414</v>
+        <v>42.70573385644197</v>
       </c>
       <c r="D4" t="n">
-        <v>2.17814861066339</v>
+        <v>2.186646974979536</v>
       </c>
       <c r="E4" t="n">
-        <v>6.473354782443094</v>
+        <v>6.523948093045484</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443892703580273</v>
+        <v>0.7444650621648846</v>
       </c>
       <c r="G4" t="n">
-        <v>33.20378776742323</v>
+        <v>33.33994510622401</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24190643646925</v>
+        <v>34.24539285958468</v>
       </c>
       <c r="I4" t="n">
-        <v>5.422420956974532</v>
+        <v>5.465885106058012</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65243293973767</v>
+        <v>4.652906638530529</v>
       </c>
       <c r="K4" t="n">
-        <v>13.08355923593081</v>
+        <v>12.84081015941285</v>
       </c>
       <c r="L4" t="n">
-        <v>44.22479252299255</v>
+        <v>44.27163987940766</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8196277285075</v>
+        <v>99.81818389526248</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.44748719764733</v>
+        <v>85.96831608354009</v>
       </c>
       <c r="C5" t="n">
-        <v>41.8838408862679</v>
+        <v>42.36328218854156</v>
       </c>
       <c r="D5" t="n">
-        <v>2.105415620538513</v>
+        <v>2.12848015066548</v>
       </c>
       <c r="E5" t="n">
-        <v>7.011639691451602</v>
+        <v>7.110898893183144</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457037618136586</v>
+        <v>0.7457822011124809</v>
       </c>
       <c r="G5" t="n">
-        <v>32.09504304909982</v>
+        <v>32.45307184692611</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30237304342829</v>
+        <v>34.30598125117412</v>
       </c>
       <c r="I5" t="n">
-        <v>4.526663519980081</v>
+        <v>4.562962983525742</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660648511335365</v>
+        <v>4.661138756953006</v>
       </c>
       <c r="K5" t="n">
-        <v>14.55251280235266</v>
+        <v>14.03168391645993</v>
       </c>
       <c r="L5" t="n">
-        <v>43.41302350701903</v>
+        <v>43.45320375316356</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8493771956396</v>
+        <v>99.84816985816504</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83.66931176866477</v>
+        <v>84.57145178439674</v>
       </c>
       <c r="C6" t="n">
-        <v>40.80832996058493</v>
+        <v>41.67511365156692</v>
       </c>
       <c r="D6" t="n">
-        <v>2.017605520678504</v>
+        <v>2.06025527692429</v>
       </c>
       <c r="E6" t="n">
-        <v>7.348856320277327</v>
+        <v>7.517667005030572</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468261136230362</v>
+        <v>0.7469015978774985</v>
       </c>
       <c r="G6" t="n">
-        <v>30.75646224459725</v>
+        <v>31.41284287012403</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35400122665966</v>
+        <v>34.35747350236493</v>
       </c>
       <c r="I6" t="n">
-        <v>3.777897132685011</v>
+        <v>3.80817654534106</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667663210143975</v>
+        <v>4.668134986734366</v>
       </c>
       <c r="K6" t="n">
-        <v>16.33068823133523</v>
+        <v>15.42854821560325</v>
       </c>
       <c r="L6" t="n">
-        <v>42.73524115474706</v>
+        <v>42.76958916106524</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87425934666722</v>
+        <v>99.87325102823542</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>81.71278710903357</v>
+        <v>82.9303090561632</v>
       </c>
       <c r="C7" t="n">
-        <v>39.43793347464005</v>
+        <v>40.62543743079798</v>
       </c>
       <c r="D7" t="n">
-        <v>1.921688468092265</v>
+        <v>1.980295051863795</v>
       </c>
       <c r="E7" t="n">
-        <v>7.524874047346848</v>
+        <v>7.755489012769996</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477864761603576</v>
+        <v>0.7478555333545132</v>
       </c>
       <c r="G7" t="n">
-        <v>29.29429871647128</v>
+        <v>30.19368424749215</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39817790337645</v>
+        <v>34.40135453430759</v>
       </c>
       <c r="I7" t="n">
-        <v>3.152296021584133</v>
+        <v>3.177533592909437</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673665476002235</v>
+        <v>4.674097083465708</v>
       </c>
       <c r="K7" t="n">
-        <v>18.28721289096644</v>
+        <v>17.06969094383681</v>
       </c>
       <c r="L7" t="n">
-        <v>42.16991204737448</v>
+        <v>42.19908894355017</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89505841298097</v>
+        <v>99.89421731818496</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>86.54546649349673</v>
+        <v>87.83220557682776</v>
       </c>
       <c r="C8" t="n">
-        <v>41.63531024344023</v>
+        <v>42.98790745998409</v>
       </c>
       <c r="D8" t="n">
-        <v>1.925879398364434</v>
+        <v>1.984499650329193</v>
       </c>
       <c r="E8" t="n">
-        <v>9.290086466484199</v>
+        <v>9.626426826662179</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494172925138377</v>
+        <v>0.7494433938225391</v>
       </c>
       <c r="G8" t="n">
-        <v>29.76072779856973</v>
+        <v>30.71881029601596</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47319545563654</v>
+        <v>34.47439611583679</v>
       </c>
       <c r="I8" t="n">
-        <v>5.662302003716521</v>
+        <v>5.594608082770231</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683858078211485</v>
+        <v>4.684021211390871</v>
       </c>
       <c r="K8" t="n">
-        <v>13.45453350650326</v>
+        <v>12.16779442317222</v>
       </c>
       <c r="L8" t="n">
-        <v>44.72182357680884</v>
+        <v>44.65820629429304</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81166732675233</v>
+        <v>99.81390817744935</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.08957082048342</v>
+        <v>85.692279518039</v>
       </c>
       <c r="C9" t="n">
-        <v>40.05664611676839</v>
+        <v>41.71628300842586</v>
       </c>
       <c r="D9" t="n">
-        <v>1.813846539439601</v>
+        <v>1.887599015171675</v>
       </c>
       <c r="E9" t="n">
-        <v>9.537565227637215</v>
+        <v>9.934821076330191</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508216743168221</v>
+        <v>0.7508050035020943</v>
       </c>
       <c r="G9" t="n">
-        <v>28.02947742962706</v>
+        <v>29.21884922095431</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53779701857382</v>
+        <v>34.53703016109633</v>
       </c>
       <c r="I9" t="n">
-        <v>4.727427466408771</v>
+        <v>4.670643769096296</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692635464480138</v>
+        <v>4.692531271888091</v>
       </c>
       <c r="K9" t="n">
-        <v>15.91042917951659</v>
+        <v>14.30772048196099</v>
       </c>
       <c r="L9" t="n">
-        <v>43.87563853694512</v>
+        <v>43.82059072953619</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84271383323009</v>
+        <v>99.84459421992305</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>81.57666433130959</v>
+        <v>83.25872299223795</v>
       </c>
       <c r="C10" t="n">
-        <v>38.27539152995921</v>
+        <v>40.0072183136428</v>
       </c>
       <c r="D10" t="n">
-        <v>1.700842359731997</v>
+        <v>1.778444474511042</v>
       </c>
       <c r="E10" t="n">
-        <v>9.601012603286263</v>
+        <v>10.0100312790052</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520322526509671</v>
+        <v>0.7519767912033017</v>
       </c>
       <c r="G10" t="n">
-        <v>26.28321718340666</v>
+        <v>27.52920537196369</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59348362194449</v>
+        <v>34.59093239535187</v>
       </c>
       <c r="I10" t="n">
-        <v>3.945874731220658</v>
+        <v>3.898277735182198</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700201579068544</v>
+        <v>4.699854945020637</v>
       </c>
       <c r="K10" t="n">
-        <v>18.42333566869041</v>
+        <v>16.74127700776206</v>
       </c>
       <c r="L10" t="n">
-        <v>43.16995537172794</v>
+        <v>43.12176457389801</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86868257037756</v>
+        <v>99.87025989530287</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>78.97296658872351</v>
+        <v>80.67820961102082</v>
       </c>
       <c r="C11" t="n">
-        <v>36.28144481360379</v>
+        <v>38.03057199868588</v>
       </c>
       <c r="D11" t="n">
-        <v>1.58521701698212</v>
+        <v>1.663954256077169</v>
       </c>
       <c r="E11" t="n">
-        <v>9.497123873813937</v>
+        <v>9.907774582250077</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530774588792646</v>
+        <v>0.7529874434806033</v>
       </c>
       <c r="G11" t="n">
-        <v>24.49645195027847</v>
+        <v>25.75696857653963</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64156310844617</v>
+        <v>34.63742240010775</v>
       </c>
       <c r="I11" t="n">
-        <v>3.292799062328147</v>
+        <v>3.252930830811825</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706734117995404</v>
+        <v>4.706171521753772</v>
       </c>
       <c r="K11" t="n">
-        <v>21.02703341127648</v>
+        <v>19.32179038897917</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58191414369691</v>
+        <v>42.53935211969101</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89039236857718</v>
+        <v>99.89171450735606</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>76.42627679595533</v>
+        <v>77.97630553125275</v>
       </c>
       <c r="C12" t="n">
-        <v>34.24251371028674</v>
+        <v>35.83157672730326</v>
       </c>
       <c r="D12" t="n">
-        <v>1.473512467375978</v>
+        <v>1.545305591263996</v>
       </c>
       <c r="E12" t="n">
-        <v>9.285776858337776</v>
+        <v>9.65361839340604</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539798186958455</v>
+        <v>0.7538610200175381</v>
       </c>
       <c r="G12" t="n">
-        <v>22.77027496457859</v>
+        <v>23.92036163853043</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68307166000889</v>
+        <v>34.67760692080675</v>
       </c>
       <c r="I12" t="n">
-        <v>2.747287160109228</v>
+        <v>2.713920592118379</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712373866849035</v>
+        <v>4.711631375109614</v>
       </c>
       <c r="K12" t="n">
-        <v>23.57372320404466</v>
+        <v>22.02369446874726</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09229644504836</v>
+        <v>42.0543696142047</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90853335937976</v>
+        <v>99.90964081025521</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>73.91086762523659</v>
+        <v>75.24863642153225</v>
       </c>
       <c r="C13" t="n">
-        <v>32.14970259939571</v>
+        <v>33.52241094906951</v>
       </c>
       <c r="D13" t="n">
-        <v>1.364377357855503</v>
+        <v>1.426713051883941</v>
       </c>
       <c r="E13" t="n">
-        <v>8.9799915618886</v>
+        <v>9.290074977176538</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547591132131355</v>
+        <v>0.754617021414659</v>
       </c>
       <c r="G13" t="n">
-        <v>21.08380368789102</v>
+        <v>22.08462348703497</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71891920780423</v>
+        <v>34.71238298507431</v>
       </c>
       <c r="I13" t="n">
-        <v>2.291772239001994</v>
+        <v>2.263868515106221</v>
       </c>
       <c r="J13" t="n">
-        <v>4.717244457582097</v>
+        <v>4.71635638384162</v>
       </c>
       <c r="K13" t="n">
-        <v>26.08913237476342</v>
+        <v>24.75136357846775</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68485149361562</v>
+        <v>41.65083878934834</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92368646777474</v>
+        <v>99.9246133168856</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>81.56973870546798</v>
+        <v>82.60399027693794</v>
       </c>
       <c r="C14" t="n">
-        <v>36.97251763883171</v>
+        <v>38.13270952372527</v>
       </c>
       <c r="D14" t="n">
-        <v>1.366002799388429</v>
+        <v>1.428384122264785</v>
       </c>
       <c r="E14" t="n">
-        <v>11.63127965250804</v>
+        <v>11.83385649985661</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556582902647834</v>
+        <v>0.7555008839066305</v>
       </c>
       <c r="G14" t="n">
-        <v>23.26362384995726</v>
+        <v>24.1596318282247</v>
       </c>
       <c r="H14" t="n">
-        <v>36.91498347048142</v>
+        <v>36.80218187916865</v>
       </c>
       <c r="I14" t="n">
-        <v>2.915326328713168</v>
+        <v>2.90255453910011</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722864314154895</v>
+        <v>4.721880524416441</v>
       </c>
       <c r="K14" t="n">
-        <v>18.43026129453199</v>
+        <v>17.39600972306206</v>
       </c>
       <c r="L14" t="n">
-        <v>44.50015915638163</v>
+        <v>44.37464212545166</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90293808974533</v>
+        <v>99.903361372239</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>80.76740539417231</v>
+        <v>81.61012780602073</v>
       </c>
       <c r="C15" t="n">
-        <v>36.61228157119061</v>
+        <v>37.57287933539698</v>
       </c>
       <c r="D15" t="n">
-        <v>1.336821781511277</v>
+        <v>1.39024599629515</v>
       </c>
       <c r="E15" t="n">
-        <v>11.78922916228718</v>
+        <v>11.93519925219871</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564187834401837</v>
+        <v>0.7562480171818912</v>
       </c>
       <c r="G15" t="n">
-        <v>22.76665837978627</v>
+        <v>23.52834280771692</v>
       </c>
       <c r="H15" t="n">
-        <v>36.95213464497522</v>
+        <v>36.85235417009854</v>
       </c>
       <c r="I15" t="n">
-        <v>2.438525245671026</v>
+        <v>2.421187455142711</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727617396501147</v>
+        <v>4.726550107386821</v>
       </c>
       <c r="K15" t="n">
-        <v>19.2325946058277</v>
+        <v>18.38987219397928</v>
       </c>
       <c r="L15" t="n">
-        <v>44.07392137013183</v>
+        <v>43.95662195564872</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91879754715013</v>
+        <v>99.91937348502498</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.18719571282492</v>
+        <v>78.85935909601457</v>
       </c>
       <c r="C16" t="n">
-        <v>34.40760248757628</v>
+        <v>35.19554339882297</v>
       </c>
       <c r="D16" t="n">
-        <v>1.241797849455613</v>
+        <v>1.287576070131228</v>
       </c>
       <c r="E16" t="n">
-        <v>11.29020520558258</v>
+        <v>11.39034563428783</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570746686438906</v>
+        <v>0.7568935338579864</v>
       </c>
       <c r="G16" t="n">
-        <v>21.14835934476486</v>
+        <v>21.79077030237241</v>
       </c>
       <c r="H16" t="n">
-        <v>36.98417557109924</v>
+        <v>36.88381052916287</v>
       </c>
       <c r="I16" t="n">
-        <v>2.033866394254412</v>
+        <v>2.019378439589816</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731716679024315</v>
+        <v>4.730584586612416</v>
       </c>
       <c r="K16" t="n">
-        <v>21.81280428717508</v>
+        <v>21.14064090398546</v>
       </c>
       <c r="L16" t="n">
-        <v>43.71185641286889</v>
+        <v>43.59656049010428</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93226318762026</v>
+        <v>99.9327447929127</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.19294554250934</v>
+        <v>80.79337262094964</v>
       </c>
       <c r="C17" t="n">
-        <v>35.85437134487418</v>
+        <v>36.58325834731638</v>
       </c>
       <c r="D17" t="n">
-        <v>1.242838786452202</v>
+        <v>1.288648847349662</v>
       </c>
       <c r="E17" t="n">
-        <v>12.1767845637127</v>
+        <v>12.24752549454969</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577092864539609</v>
+        <v>0.7575241592313048</v>
       </c>
       <c r="G17" t="n">
-        <v>21.7070936335708</v>
+        <v>22.32004013161621</v>
       </c>
       <c r="H17" t="n">
-        <v>37.55618423221014</v>
+        <v>37.42565551422683</v>
       </c>
       <c r="I17" t="n">
-        <v>2.016651999772283</v>
+        <v>2.019452478780291</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735683040337254</v>
+        <v>4.734525995195656</v>
       </c>
       <c r="K17" t="n">
-        <v>19.80705445749067</v>
+        <v>19.20662737905037</v>
       </c>
       <c r="L17" t="n">
-        <v>44.27140876572994</v>
+        <v>44.14285522961486</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93283456809479</v>
+        <v>99.93274095598161</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>77.62266133045189</v>
+        <v>78.16359449801482</v>
       </c>
       <c r="C18" t="n">
-        <v>33.59423261365613</v>
+        <v>34.26444002075378</v>
       </c>
       <c r="D18" t="n">
-        <v>1.152729960183101</v>
+        <v>1.194993960129879</v>
       </c>
       <c r="E18" t="n">
-        <v>11.5742309855931</v>
+        <v>11.63809536134558</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582564990344212</v>
+        <v>0.7580682043217949</v>
       </c>
       <c r="G18" t="n">
-        <v>20.13327669902041</v>
+        <v>20.69789081951557</v>
       </c>
       <c r="H18" t="n">
-        <v>37.58330705735345</v>
+        <v>37.45253418719423</v>
       </c>
       <c r="I18" t="n">
-        <v>1.68175701030227</v>
+        <v>1.684085688496535</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739103118965131</v>
+        <v>4.737926277011219</v>
       </c>
       <c r="K18" t="n">
-        <v>22.37733866954812</v>
+        <v>21.83640550198517</v>
       </c>
       <c r="L18" t="n">
-        <v>43.97241060569097</v>
+        <v>43.84305857507272</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94398188889522</v>
+        <v>99.94390409781168</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.61442607314449</v>
+        <v>77.14201728940672</v>
       </c>
       <c r="C19" t="n">
-        <v>32.82459508489316</v>
+        <v>33.4880907892891</v>
       </c>
       <c r="D19" t="n">
-        <v>1.117267747526454</v>
+        <v>1.15874593268026</v>
       </c>
       <c r="E19" t="n">
-        <v>11.45499217660698</v>
+        <v>11.52126177870934</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758725276773997</v>
+        <v>0.758532403214514</v>
       </c>
       <c r="G19" t="n">
-        <v>19.51390306908337</v>
+        <v>20.07005692277063</v>
       </c>
       <c r="H19" t="n">
-        <v>37.60654222612624</v>
+        <v>37.47546804037539</v>
       </c>
       <c r="I19" t="n">
-        <v>1.420962597189968</v>
+        <v>1.417124691565879</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742032979837481</v>
+        <v>4.740827520090714</v>
       </c>
       <c r="K19" t="n">
-        <v>23.38557392685551</v>
+        <v>22.85798271059327</v>
       </c>
       <c r="L19" t="n">
-        <v>43.74249483302769</v>
+        <v>43.606717918314</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95266384477637</v>
+        <v>99.95279141819637</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>73.88879010436702</v>
+        <v>74.46217985103237</v>
       </c>
       <c r="C20" t="n">
-        <v>30.31660821748972</v>
+        <v>31.02558247282899</v>
       </c>
       <c r="D20" t="n">
-        <v>1.022905195684491</v>
+        <v>1.06449204933541</v>
       </c>
       <c r="E20" t="n">
-        <v>10.68498423368951</v>
+        <v>10.78103451855318</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591308023073055</v>
+        <v>0.7589336149314815</v>
       </c>
       <c r="G20" t="n">
-        <v>17.86579168837619</v>
+        <v>18.43753269932182</v>
       </c>
       <c r="H20" t="n">
-        <v>37.62664227229444</v>
+        <v>37.49528999763513</v>
       </c>
       <c r="I20" t="n">
-        <v>1.184768397594419</v>
+        <v>1.1815618779336</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744567514420658</v>
+        <v>4.743335093321761</v>
       </c>
       <c r="K20" t="n">
-        <v>26.11120989563297</v>
+        <v>25.53782014896762</v>
       </c>
       <c r="L20" t="n">
-        <v>43.53271070362203</v>
+        <v>43.39723280343767</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96052881674473</v>
+        <v>99.96063542523429</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.21118641485423</v>
+        <v>81.07509494216029</v>
       </c>
       <c r="C21" t="n">
-        <v>34.3378774749718</v>
+        <v>35.19950911102423</v>
       </c>
       <c r="D21" t="n">
-        <v>1.023576634211163</v>
+        <v>1.065210384285851</v>
       </c>
       <c r="E21" t="n">
-        <v>12.82747239548285</v>
+        <v>13.00524728845052</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596290984051283</v>
+        <v>0.7594457545392974</v>
       </c>
       <c r="G21" t="n">
-        <v>19.74973884902604</v>
+        <v>20.39335883216202</v>
       </c>
       <c r="H21" t="n">
-        <v>39.52356052396799</v>
+        <v>39.46397658645802</v>
       </c>
       <c r="I21" t="n">
-        <v>1.579527048729011</v>
+        <v>1.641320130393974</v>
       </c>
       <c r="J21" t="n">
-        <v>4.74768186503205</v>
+        <v>4.746535965870611</v>
       </c>
       <c r="K21" t="n">
-        <v>19.78881358514577</v>
+        <v>18.9249050578397</v>
       </c>
       <c r="L21" t="n">
-        <v>45.82069257582242</v>
+        <v>45.82091205479438</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94738363593999</v>
+        <v>99.94532622365833</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_67_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_67_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.33047421029313</v>
+        <v>44.94032001970282</v>
       </c>
       <c r="M2" t="n">
-        <v>100.0191087381132</v>
+        <v>100.536846408188</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.03687563122104</v>
+        <v>87.9351763865381</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95358149053691</v>
+        <v>45.88548665164726</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228736271997047</v>
+        <v>2.228526841209489</v>
       </c>
       <c r="E3" t="n">
-        <v>5.721007473542237</v>
+        <v>5.676639169362953</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429120906656823</v>
+        <v>0.7428422804031629</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98168328718325</v>
+        <v>33.95909113617257</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17395617062138</v>
+        <v>34.17074489854549</v>
       </c>
       <c r="I3" t="n">
-        <v>6.545379770550918</v>
+        <v>6.514567808324657</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643200566660514</v>
+        <v>4.642764252519768</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96312436877897</v>
+        <v>12.0648236134619</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84834916840399</v>
+        <v>48.81582877570082</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7650550277199</v>
+        <v>106.76613904081</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.15918984058713</v>
+        <v>86.94750815949287</v>
       </c>
       <c r="C4" t="n">
-        <v>42.70573385644197</v>
+        <v>42.52423228459247</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186646974979536</v>
+        <v>2.180489241962334</v>
       </c>
       <c r="E4" t="n">
-        <v>6.523948093045484</v>
+        <v>6.460963010246728</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444650621648846</v>
+        <v>0.7443915514456346</v>
       </c>
       <c r="G4" t="n">
-        <v>33.33994510622401</v>
+        <v>33.22707697299036</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24539285958468</v>
+        <v>34.24201136649919</v>
       </c>
       <c r="I4" t="n">
-        <v>5.465885106058012</v>
+        <v>5.440128819813395</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652906638530529</v>
+        <v>4.652447196535217</v>
       </c>
       <c r="K4" t="n">
-        <v>12.84081015941285</v>
+        <v>13.05249184050714</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27163987940766</v>
+        <v>44.24231565800248</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81818389526248</v>
+        <v>99.81903978310208</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.96831608354009</v>
+        <v>85.65185545249034</v>
       </c>
       <c r="C5" t="n">
-        <v>42.36328218854156</v>
+        <v>42.07284151683882</v>
       </c>
       <c r="D5" t="n">
-        <v>2.12848015066548</v>
+        <v>2.116746939153473</v>
       </c>
       <c r="E5" t="n">
-        <v>7.110898893183144</v>
+        <v>7.028998352135134</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457822011124809</v>
+        <v>0.7457071949957842</v>
       </c>
       <c r="G5" t="n">
-        <v>32.45307184692611</v>
+        <v>32.25574890536843</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30598125117412</v>
+        <v>34.30253096980607</v>
       </c>
       <c r="I5" t="n">
-        <v>4.562962983525742</v>
+        <v>4.541453122307781</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661138756953006</v>
+        <v>4.660669968723652</v>
       </c>
       <c r="K5" t="n">
-        <v>14.03168391645993</v>
+        <v>14.34814454750968</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45320375316356</v>
+        <v>43.42789924621223</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84816985816504</v>
+        <v>99.84888531056073</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.57145178439674</v>
+        <v>84.10088162287127</v>
       </c>
       <c r="C6" t="n">
-        <v>41.67511365156692</v>
+        <v>41.22698494013207</v>
       </c>
       <c r="D6" t="n">
-        <v>2.06025527692429</v>
+        <v>2.040510592307725</v>
       </c>
       <c r="E6" t="n">
-        <v>7.517667005030572</v>
+        <v>7.407548248647172</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469015978774985</v>
+        <v>0.7468274375123597</v>
       </c>
       <c r="G6" t="n">
-        <v>31.41284287012403</v>
+        <v>31.09403211445981</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35747350236493</v>
+        <v>34.35406212556855</v>
       </c>
       <c r="I6" t="n">
-        <v>3.80817654534106</v>
+        <v>3.790229619923406</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668134986734366</v>
+        <v>4.667671484452249</v>
       </c>
       <c r="K6" t="n">
-        <v>15.42854821560325</v>
+        <v>15.89911837712873</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76958916106524</v>
+        <v>42.74774520711954</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87325102823542</v>
+        <v>99.87384852438035</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.9303090561632</v>
+        <v>82.27453041222283</v>
       </c>
       <c r="C7" t="n">
-        <v>40.62543743079798</v>
+        <v>39.98898796282356</v>
       </c>
       <c r="D7" t="n">
-        <v>1.980295051863795</v>
+        <v>1.95108585646238</v>
       </c>
       <c r="E7" t="n">
-        <v>7.755489012769996</v>
+        <v>7.610010061117889</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478555333545132</v>
+        <v>0.7477843538782765</v>
       </c>
       <c r="G7" t="n">
-        <v>30.19368424749215</v>
+        <v>29.73134592273681</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40135453430759</v>
+        <v>34.39808027840072</v>
       </c>
       <c r="I7" t="n">
-        <v>3.177533592909437</v>
+        <v>3.162571727887523</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674097083465708</v>
+        <v>4.673652211739229</v>
       </c>
       <c r="K7" t="n">
-        <v>17.06969094383681</v>
+        <v>17.72546958777716</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19908894355017</v>
+        <v>42.1802582932903</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89421731818496</v>
+        <v>99.89471584389102</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.83220557682776</v>
+        <v>87.11093204671701</v>
       </c>
       <c r="C8" t="n">
-        <v>42.98790745998409</v>
+        <v>42.25859450350867</v>
       </c>
       <c r="D8" t="n">
-        <v>1.984499650329193</v>
+        <v>1.955271343286223</v>
       </c>
       <c r="E8" t="n">
-        <v>9.626426826662179</v>
+        <v>9.419871821773297</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494433938225391</v>
+        <v>0.7493885075601183</v>
       </c>
       <c r="G8" t="n">
-        <v>30.71881029601596</v>
+        <v>30.22471634564992</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47439611583679</v>
+        <v>34.47187134776544</v>
       </c>
       <c r="I8" t="n">
-        <v>5.594608082770231</v>
+        <v>5.606134508431285</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684021211390871</v>
+        <v>4.683678172250739</v>
       </c>
       <c r="K8" t="n">
-        <v>12.16779442317222</v>
+        <v>12.88906795328298</v>
       </c>
       <c r="L8" t="n">
-        <v>44.65820629429304</v>
+        <v>44.6658664124642</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81390817744935</v>
+        <v>99.81352886925585</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.692279518039</v>
+        <v>84.810208510149</v>
       </c>
       <c r="C9" t="n">
-        <v>41.71628300842586</v>
+        <v>40.82715427453923</v>
       </c>
       <c r="D9" t="n">
-        <v>1.887599015171675</v>
+        <v>1.850530915474799</v>
       </c>
       <c r="E9" t="n">
-        <v>9.934821076330191</v>
+        <v>9.695328067533199</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508050035020943</v>
+        <v>0.750767043464678</v>
       </c>
       <c r="G9" t="n">
-        <v>29.21884922095431</v>
+        <v>28.60563174575922</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53703016109633</v>
+        <v>34.5352839993752</v>
       </c>
       <c r="I9" t="n">
-        <v>4.670643769096296</v>
+        <v>4.680372716887677</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692531271888091</v>
+        <v>4.692294021654238</v>
       </c>
       <c r="K9" t="n">
-        <v>14.30772048196099</v>
+        <v>15.18979148985099</v>
       </c>
       <c r="L9" t="n">
-        <v>43.82059072953619</v>
+        <v>43.82732827704225</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84459421992305</v>
+        <v>99.84427404143247</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.25872299223795</v>
+        <v>82.36082580102092</v>
       </c>
       <c r="C10" t="n">
-        <v>40.0072183136428</v>
+        <v>39.10292682933822</v>
       </c>
       <c r="D10" t="n">
-        <v>1.778444474511042</v>
+        <v>1.740389279977318</v>
       </c>
       <c r="E10" t="n">
-        <v>10.0100312790052</v>
+        <v>9.769351959093443</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519767912033017</v>
+        <v>0.7519540375130218</v>
       </c>
       <c r="G10" t="n">
-        <v>27.52920537196369</v>
+        <v>26.9030549130408</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59093239535187</v>
+        <v>34.58988572559901</v>
       </c>
       <c r="I10" t="n">
-        <v>3.898277735182198</v>
+        <v>3.906477151340955</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699854945020637</v>
+        <v>4.699712734456387</v>
       </c>
       <c r="K10" t="n">
-        <v>16.74127700776206</v>
+        <v>17.63917419897907</v>
       </c>
       <c r="L10" t="n">
-        <v>43.12176457389801</v>
+        <v>43.12788861843583</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87025989530287</v>
+        <v>99.86998964675311</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.67820961102082</v>
+        <v>79.85718705182072</v>
       </c>
       <c r="C11" t="n">
-        <v>38.03057199868588</v>
+        <v>37.20367771144393</v>
       </c>
       <c r="D11" t="n">
-        <v>1.663954256077169</v>
+        <v>1.629169351198333</v>
       </c>
       <c r="E11" t="n">
-        <v>9.907774582250077</v>
+        <v>9.688344082879196</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529874434806033</v>
+        <v>0.7529772141470231</v>
       </c>
       <c r="G11" t="n">
-        <v>25.75696857653963</v>
+        <v>25.18380975002503</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63742240010775</v>
+        <v>34.63695185076307</v>
       </c>
       <c r="I11" t="n">
-        <v>3.252930830811825</v>
+        <v>3.259827214389165</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706171521753772</v>
+        <v>4.706107588418895</v>
       </c>
       <c r="K11" t="n">
-        <v>19.32179038897917</v>
+        <v>20.1428129481793</v>
       </c>
       <c r="L11" t="n">
-        <v>42.53935211969101</v>
+        <v>42.54499608617286</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89171450735606</v>
+        <v>99.89148674579609</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.97630553125275</v>
+        <v>77.2654768128852</v>
       </c>
       <c r="C12" t="n">
-        <v>35.83157672730326</v>
+        <v>35.11534393909037</v>
       </c>
       <c r="D12" t="n">
-        <v>1.545305591263996</v>
+        <v>1.515268945996751</v>
       </c>
       <c r="E12" t="n">
-        <v>9.65361839340604</v>
+        <v>9.46428617233423</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538610200175381</v>
+        <v>0.7538606961202717</v>
       </c>
       <c r="G12" t="n">
-        <v>23.92036163853043</v>
+        <v>23.4231296016184</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67760692080675</v>
+        <v>34.6775920215325</v>
       </c>
       <c r="I12" t="n">
-        <v>2.713920592118379</v>
+        <v>2.719710024531355</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711631375109614</v>
+        <v>4.711629350751699</v>
       </c>
       <c r="K12" t="n">
-        <v>22.02369446874726</v>
+        <v>22.73452318711479</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0543696142047</v>
+        <v>42.0595821178396</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90964081025521</v>
+        <v>99.90944924404475</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.24863642153225</v>
+        <v>74.72132846947284</v>
       </c>
       <c r="C13" t="n">
-        <v>33.52241094906951</v>
+        <v>32.99013457606442</v>
       </c>
       <c r="D13" t="n">
-        <v>1.426713051883941</v>
+        <v>1.404631895230682</v>
       </c>
       <c r="E13" t="n">
-        <v>9.290074977176538</v>
+        <v>9.151373065958426</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754617021414659</v>
+        <v>0.7546236634402554</v>
       </c>
       <c r="G13" t="n">
-        <v>22.08462348703497</v>
+        <v>21.71289460625277</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71238298507431</v>
+        <v>34.71268851825175</v>
       </c>
       <c r="I13" t="n">
-        <v>2.263868515106221</v>
+        <v>2.268718823837363</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71635638384162</v>
+        <v>4.716397896501597</v>
       </c>
       <c r="K13" t="n">
-        <v>24.75136357846775</v>
+        <v>25.27867153052715</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65083878934834</v>
+        <v>41.655646392727</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9246133168856</v>
+        <v>99.92445249931858</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.60399027693794</v>
+        <v>82.16947856051533</v>
       </c>
       <c r="C14" t="n">
-        <v>38.13270952372527</v>
+        <v>37.75187472452182</v>
       </c>
       <c r="D14" t="n">
-        <v>1.428384122264785</v>
+        <v>1.406207743761893</v>
       </c>
       <c r="E14" t="n">
-        <v>11.83385649985661</v>
+        <v>11.75893171764693</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555008839066305</v>
+        <v>0.755470271434625</v>
       </c>
       <c r="G14" t="n">
-        <v>24.1596318282247</v>
+        <v>23.87361860513187</v>
       </c>
       <c r="H14" t="n">
-        <v>36.80218187916865</v>
+        <v>36.88799691195473</v>
       </c>
       <c r="I14" t="n">
-        <v>2.90255453910011</v>
+        <v>2.76556411411888</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721880524416441</v>
+        <v>4.721689196466406</v>
       </c>
       <c r="K14" t="n">
-        <v>17.39600972306206</v>
+        <v>17.83052143948466</v>
       </c>
       <c r="L14" t="n">
-        <v>44.37464212545166</v>
+        <v>44.32552167197878</v>
       </c>
       <c r="M14" t="n">
-        <v>99.903361372239</v>
+        <v>99.90791783598526</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.61012780602073</v>
+        <v>81.2806336415214</v>
       </c>
       <c r="C15" t="n">
-        <v>37.57287933539698</v>
+        <v>37.28528766576817</v>
       </c>
       <c r="D15" t="n">
-        <v>1.39024599629515</v>
+        <v>1.373281348816277</v>
       </c>
       <c r="E15" t="n">
-        <v>11.93519925219871</v>
+        <v>11.87227134983849</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562480171818912</v>
+        <v>0.7561849688148609</v>
       </c>
       <c r="G15" t="n">
-        <v>23.52834280771692</v>
+        <v>23.31882299106033</v>
       </c>
       <c r="H15" t="n">
-        <v>36.85235417009854</v>
+        <v>36.92709991110717</v>
       </c>
       <c r="I15" t="n">
-        <v>2.421187455142711</v>
+        <v>2.30681701679139</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726550107386821</v>
+        <v>4.726156055092881</v>
       </c>
       <c r="K15" t="n">
-        <v>18.38987219397928</v>
+        <v>18.71936635847859</v>
       </c>
       <c r="L15" t="n">
-        <v>43.95662195564872</v>
+        <v>43.91852475036105</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91937348502498</v>
+        <v>99.92317877460781</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.85935909601457</v>
+        <v>78.62803970193991</v>
       </c>
       <c r="C16" t="n">
-        <v>35.19554339882297</v>
+        <v>34.98835797128059</v>
       </c>
       <c r="D16" t="n">
-        <v>1.287576070131228</v>
+        <v>1.274694295067461</v>
       </c>
       <c r="E16" t="n">
-        <v>11.39034563428783</v>
+        <v>11.34062059874566</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568935338579864</v>
+        <v>0.7568017275543066</v>
       </c>
       <c r="G16" t="n">
-        <v>21.79077030237241</v>
+        <v>21.64477851535229</v>
       </c>
       <c r="H16" t="n">
-        <v>36.88381052916287</v>
+        <v>36.95721835108127</v>
       </c>
       <c r="I16" t="n">
-        <v>2.019378439589816</v>
+        <v>1.923915416924518</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730584586612416</v>
+        <v>4.730010797214417</v>
       </c>
       <c r="K16" t="n">
-        <v>21.14064090398546</v>
+        <v>21.37196029806009</v>
       </c>
       <c r="L16" t="n">
-        <v>43.59656049010428</v>
+        <v>43.57560348019287</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9327447929127</v>
+        <v>99.93592174953355</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.79337262094964</v>
+        <v>80.54063149196833</v>
       </c>
       <c r="C17" t="n">
-        <v>36.58325834731638</v>
+        <v>36.382360315387</v>
       </c>
       <c r="D17" t="n">
-        <v>1.288648847349662</v>
+        <v>1.275688159853106</v>
       </c>
       <c r="E17" t="n">
-        <v>12.24752549454969</v>
+        <v>12.18971921936488</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575241592313048</v>
+        <v>0.7573917973378164</v>
       </c>
       <c r="G17" t="n">
-        <v>22.32004013161621</v>
+        <v>22.1879280554135</v>
       </c>
       <c r="H17" t="n">
-        <v>37.42565551422683</v>
+        <v>37.51230682802635</v>
       </c>
       <c r="I17" t="n">
-        <v>2.019452478780291</v>
+        <v>1.883898698611339</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734525995195656</v>
+        <v>4.733698733361353</v>
       </c>
       <c r="K17" t="n">
-        <v>19.20662737905037</v>
+        <v>19.45936850803167</v>
       </c>
       <c r="L17" t="n">
-        <v>44.14285522961486</v>
+        <v>44.09552347696899</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93274095598161</v>
+        <v>99.93725230038766</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.16359449801482</v>
+        <v>77.99300601692491</v>
       </c>
       <c r="C18" t="n">
-        <v>34.26444002075378</v>
+        <v>34.12475435395523</v>
       </c>
       <c r="D18" t="n">
-        <v>1.194993960129879</v>
+        <v>1.185328589012417</v>
       </c>
       <c r="E18" t="n">
-        <v>11.63809536134558</v>
+        <v>11.58812504309166</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580682043217949</v>
+        <v>0.7579003213645256</v>
       </c>
       <c r="G18" t="n">
-        <v>20.69789081951557</v>
+        <v>20.61631226401027</v>
       </c>
       <c r="H18" t="n">
-        <v>37.45253418719423</v>
+        <v>37.53749314425843</v>
       </c>
       <c r="I18" t="n">
-        <v>1.684085688496535</v>
+        <v>1.570969646659317</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737926277011219</v>
+        <v>4.736877008528286</v>
       </c>
       <c r="K18" t="n">
-        <v>21.83640550198517</v>
+        <v>22.00699398307509</v>
       </c>
       <c r="L18" t="n">
-        <v>43.84305857507272</v>
+        <v>43.81592114356381</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94390409781168</v>
+        <v>99.94766948059413</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.14201728940672</v>
+        <v>76.94807303043278</v>
       </c>
       <c r="C19" t="n">
-        <v>33.4880907892891</v>
+        <v>33.3060360738776</v>
       </c>
       <c r="D19" t="n">
-        <v>1.15874593268026</v>
+        <v>1.148278348176542</v>
       </c>
       <c r="E19" t="n">
-        <v>11.52126177870934</v>
+        <v>11.4466288313461</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758532403214514</v>
+        <v>0.7583351138498566</v>
       </c>
       <c r="G19" t="n">
-        <v>20.07005692277063</v>
+        <v>19.97190079734211</v>
       </c>
       <c r="H19" t="n">
-        <v>37.47546804037539</v>
+        <v>37.55902766466595</v>
       </c>
       <c r="I19" t="n">
-        <v>1.417124691565879</v>
+        <v>1.324307813490604</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740827520090714</v>
+        <v>4.739594461561606</v>
       </c>
       <c r="K19" t="n">
-        <v>22.85798271059327</v>
+        <v>23.05192696956723</v>
       </c>
       <c r="L19" t="n">
-        <v>43.606717918314</v>
+        <v>43.59791867256264</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95279141819637</v>
+        <v>99.95588171600747</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.46217985103237</v>
+        <v>74.25011252943803</v>
       </c>
       <c r="C20" t="n">
-        <v>31.02558247282899</v>
+        <v>30.81111423048245</v>
       </c>
       <c r="D20" t="n">
-        <v>1.06449204933541</v>
+        <v>1.05367255207395</v>
       </c>
       <c r="E20" t="n">
-        <v>10.78103451855318</v>
+        <v>10.68757243764372</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589336149314815</v>
+        <v>0.7587110081235076</v>
       </c>
       <c r="G20" t="n">
-        <v>18.43753269932182</v>
+        <v>18.32643079643599</v>
       </c>
       <c r="H20" t="n">
-        <v>37.49528999763513</v>
+        <v>37.57764505843448</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1815618779336</v>
+        <v>1.104136875954453</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743335093321761</v>
+        <v>4.741943800771924</v>
       </c>
       <c r="K20" t="n">
-        <v>25.53782014896762</v>
+        <v>25.74988747056198</v>
       </c>
       <c r="L20" t="n">
-        <v>43.39723280343767</v>
+        <v>43.40221197080307</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96063542523429</v>
+        <v>99.9632136718475</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.07509494216029</v>
+        <v>80.69890885684701</v>
       </c>
       <c r="C21" t="n">
-        <v>35.19950911102423</v>
+        <v>34.93755710576801</v>
       </c>
       <c r="D21" t="n">
-        <v>1.065210384285851</v>
+        <v>1.054307991116069</v>
       </c>
       <c r="E21" t="n">
-        <v>13.00524728845052</v>
+        <v>12.8725104867018</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594457545392974</v>
+        <v>0.7591685645012441</v>
       </c>
       <c r="G21" t="n">
-        <v>20.39335883216202</v>
+        <v>20.27263988042153</v>
       </c>
       <c r="H21" t="n">
-        <v>39.46397658645802</v>
+        <v>39.53546398565472</v>
       </c>
       <c r="I21" t="n">
-        <v>1.641320130393974</v>
+        <v>1.460014420318871</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746535965870611</v>
+        <v>4.744803528132778</v>
       </c>
       <c r="K21" t="n">
-        <v>18.9249050578397</v>
+        <v>19.30109114315299</v>
       </c>
       <c r="L21" t="n">
-        <v>45.82091205479438</v>
+        <v>45.71271393577629</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94532622365833</v>
+        <v>99.9513621846973</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_67_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_67_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>44.94032001970282</v>
+        <v>43.472332959386</v>
       </c>
       <c r="M2" t="n">
-        <v>100.536846408188</v>
+        <v>97.35865574094242</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.9351763865381</v>
+        <v>81.4696059433374</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88548665164726</v>
+        <v>43.22516149889294</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228526841209489</v>
+        <v>2.179274968866067</v>
       </c>
       <c r="E3" t="n">
-        <v>5.676639169362953</v>
+        <v>4.158272111420934</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428422804031629</v>
+        <v>0.7376278294285624</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95909113617257</v>
+        <v>32.77992765669376</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17074489854549</v>
+        <v>33.93088015371386</v>
       </c>
       <c r="I3" t="n">
-        <v>6.514567808324657</v>
+        <v>3.073449289285676</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642764252519768</v>
+        <v>4.610173933928515</v>
       </c>
       <c r="K3" t="n">
-        <v>12.0648236134619</v>
+        <v>18.53039405666262</v>
       </c>
       <c r="L3" t="n">
-        <v>48.81582877570082</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.76613904081</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.94750815949287</v>
+        <v>88.60712373929569</v>
       </c>
       <c r="C4" t="n">
-        <v>42.52423228459247</v>
+        <v>42.81965813549018</v>
       </c>
       <c r="D4" t="n">
-        <v>2.180489241962334</v>
+        <v>2.185039339817487</v>
       </c>
       <c r="E4" t="n">
-        <v>6.460963010246728</v>
+        <v>6.541491672879127</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443915514456346</v>
+        <v>0.7395789188934819</v>
       </c>
       <c r="G4" t="n">
-        <v>33.22707697299036</v>
+        <v>33.46680990654534</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24201136649919</v>
+        <v>34.02063026910016</v>
       </c>
       <c r="I4" t="n">
-        <v>5.440128819813395</v>
+        <v>7.031205388975827</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652447196535217</v>
+        <v>4.622368243084261</v>
       </c>
       <c r="K4" t="n">
-        <v>13.05249184050714</v>
+        <v>11.39287626070432</v>
       </c>
       <c r="L4" t="n">
-        <v>44.24231565800248</v>
+        <v>45.5537103936067</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81903978310208</v>
+        <v>99.76624478980119</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.65185545249034</v>
+        <v>87.51625762979208</v>
       </c>
       <c r="C5" t="n">
-        <v>42.07284151683882</v>
+        <v>42.81861003265627</v>
       </c>
       <c r="D5" t="n">
-        <v>2.116746939153473</v>
+        <v>2.133308294067376</v>
       </c>
       <c r="E5" t="n">
-        <v>7.028998352135134</v>
+        <v>7.365361713978823</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457071949957842</v>
+        <v>0.7412331392967217</v>
       </c>
       <c r="G5" t="n">
-        <v>32.25574890536843</v>
+        <v>32.67447951558297</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30253096980607</v>
+        <v>34.09672440764919</v>
       </c>
       <c r="I5" t="n">
-        <v>4.541453122307781</v>
+        <v>5.872443438612494</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660669968723652</v>
+        <v>4.63270712060451</v>
       </c>
       <c r="K5" t="n">
-        <v>14.34814454750968</v>
+        <v>12.48374237020791</v>
       </c>
       <c r="L5" t="n">
-        <v>43.42789924621223</v>
+        <v>44.50233633633094</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84888531056073</v>
+        <v>99.80468873919513</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.10088162287127</v>
+        <v>86.19543327903904</v>
       </c>
       <c r="C6" t="n">
-        <v>41.22698494013207</v>
+        <v>42.40917545642457</v>
       </c>
       <c r="D6" t="n">
-        <v>2.040510592307725</v>
+        <v>2.070413258305426</v>
       </c>
       <c r="E6" t="n">
-        <v>7.407548248647172</v>
+        <v>7.965376830430495</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468274375123597</v>
+        <v>0.7426385704826349</v>
       </c>
       <c r="G6" t="n">
-        <v>31.09403211445981</v>
+        <v>31.71115763503212</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35406212556855</v>
+        <v>34.1613742422012</v>
       </c>
       <c r="I6" t="n">
-        <v>3.790229619923406</v>
+        <v>4.902981677070708</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667671484452249</v>
+        <v>4.641491065516467</v>
       </c>
       <c r="K6" t="n">
-        <v>15.89911837712873</v>
+        <v>13.80456672096095</v>
       </c>
       <c r="L6" t="n">
-        <v>42.74774520711954</v>
+        <v>43.62313439376411</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87384852438035</v>
+        <v>99.83687657114963</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.27453041222283</v>
+        <v>84.74635981480674</v>
       </c>
       <c r="C7" t="n">
-        <v>39.98898796282356</v>
+        <v>41.7214825073893</v>
       </c>
       <c r="D7" t="n">
-        <v>1.95108585646238</v>
+        <v>2.001764373359102</v>
       </c>
       <c r="E7" t="n">
-        <v>7.610010061117889</v>
+        <v>8.383333899838609</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477843538782765</v>
+        <v>0.743833969031944</v>
       </c>
       <c r="G7" t="n">
-        <v>29.73134592273681</v>
+        <v>30.65970783230828</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39808027840072</v>
+        <v>34.21636257546942</v>
       </c>
       <c r="I7" t="n">
-        <v>3.162571727887523</v>
+        <v>4.092394858349738</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673652211739229</v>
+        <v>4.648962306449649</v>
       </c>
       <c r="K7" t="n">
-        <v>17.72546958777716</v>
+        <v>15.25364018519326</v>
       </c>
       <c r="L7" t="n">
-        <v>42.1802582932903</v>
+        <v>42.88868337194326</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89471584389102</v>
+        <v>99.86380606452582</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.11093204671701</v>
+        <v>83.15031901161375</v>
       </c>
       <c r="C8" t="n">
-        <v>42.25859450350867</v>
+        <v>40.76098744611573</v>
       </c>
       <c r="D8" t="n">
-        <v>1.955271343286223</v>
+        <v>1.926558970863691</v>
       </c>
       <c r="E8" t="n">
-        <v>9.419871821773297</v>
+        <v>8.637542053045324</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493885075601183</v>
+        <v>0.7448522819718251</v>
       </c>
       <c r="G8" t="n">
-        <v>30.22471634564992</v>
+        <v>29.50783616419023</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47187134776544</v>
+        <v>34.26320497070395</v>
       </c>
       <c r="I8" t="n">
-        <v>5.606134508431285</v>
+        <v>3.414997808514824</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683678172250739</v>
+        <v>4.655326762323905</v>
       </c>
       <c r="K8" t="n">
-        <v>12.88906795328298</v>
+        <v>16.84968098838626</v>
       </c>
       <c r="L8" t="n">
-        <v>44.6658664124642</v>
+        <v>42.27565393054385</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81352886925585</v>
+        <v>99.88632236504584</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.810208510149</v>
+        <v>81.38871982928056</v>
       </c>
       <c r="C9" t="n">
-        <v>40.82715427453923</v>
+        <v>39.52949553892049</v>
       </c>
       <c r="D9" t="n">
-        <v>1.850530915474799</v>
+        <v>1.844014924094711</v>
       </c>
       <c r="E9" t="n">
-        <v>9.695328067533199</v>
+        <v>8.742322463302395</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750767043464678</v>
+        <v>0.7457214431950728</v>
       </c>
       <c r="G9" t="n">
-        <v>28.60563174575922</v>
+        <v>28.24356331024463</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5352839993752</v>
+        <v>34.30318638697334</v>
       </c>
       <c r="I9" t="n">
-        <v>4.680372716887677</v>
+        <v>2.849152281501205</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692294021654238</v>
+        <v>4.660759019969204</v>
       </c>
       <c r="K9" t="n">
-        <v>15.18979148985099</v>
+        <v>18.61128017071944</v>
       </c>
       <c r="L9" t="n">
-        <v>43.82732827704225</v>
+        <v>41.76436324012354</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84427404143247</v>
+        <v>99.90513894976347</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.36082580102092</v>
+        <v>85.95245680676661</v>
       </c>
       <c r="C10" t="n">
-        <v>39.10292682933822</v>
+        <v>42.73902885306045</v>
       </c>
       <c r="D10" t="n">
-        <v>1.740389279977318</v>
+        <v>1.846025332921459</v>
       </c>
       <c r="E10" t="n">
-        <v>9.769351959093443</v>
+        <v>10.56955227981953</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519540375130218</v>
+        <v>0.7465344544956353</v>
       </c>
       <c r="G10" t="n">
-        <v>26.9030549130408</v>
+        <v>29.62351235277402</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58988572559901</v>
+        <v>35.68974184009141</v>
       </c>
       <c r="I10" t="n">
-        <v>3.906477151340955</v>
+        <v>2.811250206066818</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699712734456387</v>
+        <v>4.665840340597719</v>
       </c>
       <c r="K10" t="n">
-        <v>17.63917419897907</v>
+        <v>14.04754319323338</v>
       </c>
       <c r="L10" t="n">
-        <v>43.12788861843583</v>
+        <v>43.11982166631489</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86998964675311</v>
+        <v>99.90639371260872</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.85718705182072</v>
+        <v>85.70996512381765</v>
       </c>
       <c r="C11" t="n">
-        <v>37.20367771144393</v>
+        <v>42.82723769804691</v>
       </c>
       <c r="D11" t="n">
-        <v>1.629169351198333</v>
+        <v>1.829540334174358</v>
       </c>
       <c r="E11" t="n">
-        <v>9.688344082879196</v>
+        <v>10.90535760678988</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529772141470231</v>
+        <v>0.7472377321976774</v>
       </c>
       <c r="G11" t="n">
-        <v>25.18380975002503</v>
+        <v>29.38544770636254</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63695185076307</v>
+        <v>35.74983679549627</v>
       </c>
       <c r="I11" t="n">
-        <v>3.259827214389165</v>
+        <v>2.42230912256145</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706107588418895</v>
+        <v>4.670235826235483</v>
       </c>
       <c r="K11" t="n">
-        <v>20.1428129481793</v>
+        <v>14.29003487618234</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54499608617286</v>
+        <v>42.80205978183754</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89148674579609</v>
+        <v>99.91933235606679</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.2654768128852</v>
+        <v>83.84952377183882</v>
       </c>
       <c r="C12" t="n">
-        <v>35.11534393909037</v>
+        <v>41.3435738501236</v>
       </c>
       <c r="D12" t="n">
-        <v>1.515268945996751</v>
+        <v>1.75013458233728</v>
       </c>
       <c r="E12" t="n">
-        <v>9.46428617233423</v>
+        <v>10.76874503846722</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538606961202717</v>
+        <v>0.7478378463983046</v>
       </c>
       <c r="G12" t="n">
-        <v>23.4231296016184</v>
+        <v>28.11005982635394</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6775920215325</v>
+        <v>35.77854785197356</v>
       </c>
       <c r="I12" t="n">
-        <v>2.719710024531355</v>
+        <v>2.020212086319116</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711629350751699</v>
+        <v>4.673986539989403</v>
       </c>
       <c r="K12" t="n">
-        <v>22.73452318711479</v>
+        <v>16.15047622816117</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0595821178396</v>
+        <v>42.43866355719963</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90944924404475</v>
+        <v>99.9327136354844</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.72132846947284</v>
+        <v>84.97537240411499</v>
       </c>
       <c r="C13" t="n">
-        <v>32.99013457606442</v>
+        <v>42.30252190000674</v>
       </c>
       <c r="D13" t="n">
-        <v>1.404631895230682</v>
+        <v>1.751405537501383</v>
       </c>
       <c r="E13" t="n">
-        <v>9.151373065958426</v>
+        <v>11.39404748042392</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546236634402554</v>
+        <v>0.7483809294173961</v>
       </c>
       <c r="G13" t="n">
-        <v>21.71289460625277</v>
+        <v>28.43940822366835</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71268851825175</v>
+        <v>36.11346513784967</v>
       </c>
       <c r="I13" t="n">
-        <v>2.268718823837363</v>
+        <v>1.851284286395543</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716397896501597</v>
+        <v>4.677380808858724</v>
       </c>
       <c r="K13" t="n">
-        <v>25.27867153052715</v>
+        <v>15.02462759588501</v>
       </c>
       <c r="L13" t="n">
-        <v>41.655646392727</v>
+        <v>42.6111858090584</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92445249931858</v>
+        <v>99.93833530495016</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.16947856051533</v>
+        <v>83.14731890889925</v>
       </c>
       <c r="C14" t="n">
-        <v>37.75187472452182</v>
+        <v>40.76231149335025</v>
       </c>
       <c r="D14" t="n">
-        <v>1.406207743761893</v>
+        <v>1.675450691140088</v>
       </c>
       <c r="E14" t="n">
-        <v>11.75893171764693</v>
+        <v>11.15719307842018</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755470271434625</v>
+        <v>0.7488440709833953</v>
       </c>
       <c r="G14" t="n">
-        <v>23.87361860513187</v>
+        <v>27.20604973759402</v>
       </c>
       <c r="H14" t="n">
-        <v>36.88799691195473</v>
+        <v>36.1358142466259</v>
       </c>
       <c r="I14" t="n">
-        <v>2.76556411411888</v>
+        <v>1.543691640489447</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721689196466406</v>
+        <v>4.680275443646219</v>
       </c>
       <c r="K14" t="n">
-        <v>17.83052143948466</v>
+        <v>16.85268109110075</v>
       </c>
       <c r="L14" t="n">
-        <v>44.32552167197878</v>
+        <v>42.33358285203801</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90791783598526</v>
+        <v>99.94857543648902</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.2806336415214</v>
+        <v>82.30971140258995</v>
       </c>
       <c r="C15" t="n">
-        <v>37.28528766576817</v>
+        <v>40.13276468196376</v>
       </c>
       <c r="D15" t="n">
-        <v>1.373281348816277</v>
+        <v>1.639740873132238</v>
       </c>
       <c r="E15" t="n">
-        <v>11.87227134983849</v>
+        <v>11.13900377492343</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561849688148609</v>
+        <v>0.7492436685272093</v>
       </c>
       <c r="G15" t="n">
-        <v>23.31882299106033</v>
+        <v>26.62619197754206</v>
       </c>
       <c r="H15" t="n">
-        <v>36.92709991110717</v>
+        <v>36.15509700945488</v>
       </c>
       <c r="I15" t="n">
-        <v>2.30681701679139</v>
+        <v>1.317661170715083</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726156055092881</v>
+        <v>4.682772928295056</v>
       </c>
       <c r="K15" t="n">
-        <v>18.71936635847859</v>
+        <v>17.69028859741004</v>
       </c>
       <c r="L15" t="n">
-        <v>43.91852475036105</v>
+        <v>42.1330481067438</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92317877460781</v>
+        <v>99.95610138611761</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.62803970193991</v>
+        <v>80.09447624777337</v>
       </c>
       <c r="C16" t="n">
-        <v>34.98835797128059</v>
+        <v>38.121953635241</v>
       </c>
       <c r="D16" t="n">
-        <v>1.274694295067461</v>
+        <v>1.54826676390581</v>
       </c>
       <c r="E16" t="n">
-        <v>11.34062059874566</v>
+        <v>10.70069870358812</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568017275543066</v>
+        <v>0.7495862156098975</v>
       </c>
       <c r="G16" t="n">
-        <v>21.64477851535229</v>
+        <v>25.14083094693909</v>
       </c>
       <c r="H16" t="n">
-        <v>36.95721835108127</v>
+        <v>36.17162677610509</v>
       </c>
       <c r="I16" t="n">
-        <v>1.923915416924518</v>
+        <v>1.098552994063503</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730010797214417</v>
+        <v>4.684913847561857</v>
       </c>
       <c r="K16" t="n">
-        <v>21.37196029806009</v>
+        <v>19.90552375222663</v>
       </c>
       <c r="L16" t="n">
-        <v>43.57560348019287</v>
+        <v>41.93592091334585</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93592174953355</v>
+        <v>99.96339830081348</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.54063149196833</v>
+        <v>84.55545927605453</v>
       </c>
       <c r="C17" t="n">
-        <v>36.382360315387</v>
+        <v>41.11379495213669</v>
       </c>
       <c r="D17" t="n">
-        <v>1.275688159853106</v>
+        <v>1.548972474944374</v>
       </c>
       <c r="E17" t="n">
-        <v>12.18971921936488</v>
+        <v>12.28981265283605</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573917973378164</v>
+        <v>0.7499278823556054</v>
       </c>
       <c r="G17" t="n">
-        <v>22.1879280554135</v>
+        <v>26.54382190310516</v>
       </c>
       <c r="H17" t="n">
-        <v>37.51230682802635</v>
+        <v>37.57964564771976</v>
       </c>
       <c r="I17" t="n">
-        <v>1.883898698611339</v>
+        <v>1.156229450371055</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733698733361353</v>
+        <v>4.687049264722531</v>
       </c>
       <c r="K17" t="n">
-        <v>19.45936850803167</v>
+        <v>15.44454072394546</v>
       </c>
       <c r="L17" t="n">
-        <v>44.09552347696899</v>
+        <v>43.40314090148963</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93725230038766</v>
+        <v>99.96147657757177</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>77.99300601692491</v>
+        <v>86.17447905008204</v>
       </c>
       <c r="C18" t="n">
-        <v>34.12475435395523</v>
+        <v>41.82890303344259</v>
       </c>
       <c r="D18" t="n">
-        <v>1.185328589012417</v>
+        <v>1.550178818725749</v>
       </c>
       <c r="E18" t="n">
-        <v>11.58812504309166</v>
+        <v>12.875845806163</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579003213645256</v>
+        <v>0.7505119281356263</v>
       </c>
       <c r="G18" t="n">
-        <v>20.61631226401027</v>
+        <v>26.68494293860089</v>
       </c>
       <c r="H18" t="n">
-        <v>37.53749314425843</v>
+        <v>37.60891277322827</v>
       </c>
       <c r="I18" t="n">
-        <v>1.570969646659317</v>
+        <v>2.013387234380833</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736877008528286</v>
+        <v>4.690699550847662</v>
       </c>
       <c r="K18" t="n">
-        <v>22.00699398307509</v>
+        <v>13.82552094991796</v>
       </c>
       <c r="L18" t="n">
-        <v>43.81592114356381</v>
+        <v>44.27851533585889</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94766948059413</v>
+        <v>99.93293931921944</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.94807303043278</v>
+        <v>83.66438578977196</v>
       </c>
       <c r="C19" t="n">
-        <v>33.3060360738776</v>
+        <v>39.63102334720142</v>
       </c>
       <c r="D19" t="n">
-        <v>1.148278348176542</v>
+        <v>1.456503904512855</v>
       </c>
       <c r="E19" t="n">
-        <v>11.4466288313461</v>
+        <v>12.37760248142696</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583351138498566</v>
+        <v>0.7510139610522049</v>
       </c>
       <c r="G19" t="n">
-        <v>19.97190079734211</v>
+        <v>25.07241300956716</v>
       </c>
       <c r="H19" t="n">
-        <v>37.55902766466595</v>
+        <v>37.63407015109406</v>
       </c>
       <c r="I19" t="n">
-        <v>1.324307813490604</v>
+        <v>1.678945025542444</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739594461561606</v>
+        <v>4.693837256576278</v>
       </c>
       <c r="K19" t="n">
-        <v>23.05192696956723</v>
+        <v>16.33561421022804</v>
       </c>
       <c r="L19" t="n">
-        <v>43.59791867256264</v>
+        <v>43.97743501939329</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95588171600747</v>
+        <v>99.94407257682275</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.25011252943803</v>
+        <v>81.09434701464059</v>
       </c>
       <c r="C20" t="n">
-        <v>30.81111423048245</v>
+        <v>37.32068139053091</v>
       </c>
       <c r="D20" t="n">
-        <v>1.05367255207395</v>
+        <v>1.361074723748181</v>
       </c>
       <c r="E20" t="n">
-        <v>10.68757243764372</v>
+        <v>11.79995107510148</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587110081235076</v>
+        <v>0.7514461177409499</v>
       </c>
       <c r="G20" t="n">
-        <v>18.32643079643599</v>
+        <v>23.4296849496676</v>
       </c>
       <c r="H20" t="n">
-        <v>37.57764505843448</v>
+        <v>37.65572596041844</v>
       </c>
       <c r="I20" t="n">
-        <v>1.104136875954453</v>
+        <v>1.399925952082989</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741943800771924</v>
+        <v>4.696538235880935</v>
       </c>
       <c r="K20" t="n">
-        <v>25.74988747056198</v>
+        <v>18.90565298535942</v>
       </c>
       <c r="L20" t="n">
-        <v>43.40221197080307</v>
+        <v>43.72702826228904</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9632136718475</v>
+        <v>99.95336263817937</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.69890885684701</v>
+        <v>78.43725667057362</v>
       </c>
       <c r="C21" t="n">
-        <v>34.93755710576801</v>
+        <v>34.87950068220279</v>
       </c>
       <c r="D21" t="n">
-        <v>1.054307991116069</v>
+        <v>1.262864294108158</v>
       </c>
       <c r="E21" t="n">
-        <v>12.8725104867018</v>
+        <v>11.14303814941757</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7591685645012441</v>
+        <v>0.751818846906104</v>
       </c>
       <c r="G21" t="n">
-        <v>20.27263988042153</v>
+        <v>21.73908017603656</v>
       </c>
       <c r="H21" t="n">
-        <v>39.53546398565472</v>
+        <v>37.67440379635256</v>
       </c>
       <c r="I21" t="n">
-        <v>1.460014420318871</v>
+        <v>1.167183614589508</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744803528132778</v>
+        <v>4.698867793163148</v>
       </c>
       <c r="K21" t="n">
-        <v>19.30109114315299</v>
+        <v>21.56274332942638</v>
       </c>
       <c r="L21" t="n">
-        <v>45.71271393577629</v>
+        <v>43.51886915636854</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9513621846973</v>
+        <v>99.96111316799769</v>
       </c>
     </row>
   </sheetData>
